--- a/data.xlsx
+++ b/data.xlsx
@@ -1,70 +1,228 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24026"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\insert-prices\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321C550D-6061-43AB-B17F-BE979D47EBFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="prices" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="prices" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+  <si>
+    <t>N991A1</t>
+  </si>
+  <si>
+    <t>04362021D</t>
+  </si>
+  <si>
+    <t>050200945</t>
+  </si>
+  <si>
+    <t>S03601</t>
+  </si>
+  <si>
+    <t>070001317</t>
+  </si>
+  <si>
+    <t>052400004</t>
+  </si>
+  <si>
+    <t>C366C1</t>
+  </si>
+  <si>
+    <t>040500253</t>
+  </si>
+  <si>
+    <t>040500048</t>
+  </si>
+  <si>
+    <t>040500024</t>
+  </si>
+  <si>
+    <t>04290102B</t>
+  </si>
+  <si>
+    <t>E094A1</t>
+  </si>
+  <si>
+    <t>070001194</t>
+  </si>
+  <si>
+    <t>070001196</t>
+  </si>
+  <si>
+    <t>F40701</t>
+  </si>
+  <si>
+    <t>C442B2</t>
+  </si>
+  <si>
+    <t>L17801</t>
+  </si>
+  <si>
+    <t>030404024</t>
+  </si>
+  <si>
+    <t>050200510</t>
+  </si>
+  <si>
+    <t>L19201</t>
+  </si>
+  <si>
+    <t>052701001</t>
+  </si>
+  <si>
+    <t>N101301</t>
+  </si>
+  <si>
+    <t>070001213</t>
+  </si>
+  <si>
+    <t>080203144</t>
+  </si>
+  <si>
+    <t>F40501</t>
+  </si>
+  <si>
+    <t>070100054</t>
+  </si>
+  <si>
+    <t>050502058</t>
+  </si>
+  <si>
+    <t>050200944</t>
+  </si>
+  <si>
+    <t>080203119</t>
+  </si>
+  <si>
+    <t>080203118</t>
+  </si>
+  <si>
+    <t>080203116</t>
+  </si>
+  <si>
+    <t>070001165</t>
+  </si>
+  <si>
+    <t>050502037</t>
+  </si>
+  <si>
+    <t>070001195</t>
+  </si>
+  <si>
+    <t>N80601</t>
+  </si>
+  <si>
+    <t>070001092</t>
+  </si>
+  <si>
+    <t>020202351</t>
+  </si>
+  <si>
+    <t>052700001</t>
+  </si>
+  <si>
+    <t>N722A1</t>
+  </si>
+  <si>
+    <t>04388018A</t>
+  </si>
+  <si>
+    <t>F06901</t>
+  </si>
+  <si>
+    <t>050502001</t>
+  </si>
+  <si>
+    <t>04327100A</t>
+  </si>
+  <si>
+    <t>F241A2</t>
+  </si>
+  <si>
+    <t>080203142</t>
+  </si>
+  <si>
+    <t>080202012</t>
+  </si>
+  <si>
+    <t>020303091</t>
+  </si>
+  <si>
+    <t>080203141</t>
+  </si>
+  <si>
+    <t>F40401</t>
+  </si>
+  <si>
+    <t>F169I2</t>
+  </si>
+  <si>
+    <t>OBM000240</t>
+  </si>
+  <si>
+    <t>OBM000001</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <charset val="204"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <charset val="204"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <charset val="204"/>
-      <family val="2"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.7999816888943144"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -72,47 +230,44 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <colors/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -436,540 +591,433 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B52"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="21.88671875" customWidth="1" style="5" min="1" max="1"/>
-    <col width="16.88671875" customWidth="1" style="6" min="2" max="2"/>
+    <col min="1" max="1" width="17.77734375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" style="6" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>N991A1</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="n">
-        <v>1304.61</v>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>04362021D</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
+    <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5">
+        <v>1304.6099999999999</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5">
         <v>332.66</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>050200945</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
+    <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5">
         <v>1346.75</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>S03601</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5">
         <v>864.09</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>070001317</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5">
         <v>908.38</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>052400004</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5">
         <v>1582.75</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>C366C1</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5">
         <v>762.78</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>040500253</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5">
         <v>693.6</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>040500048</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5">
         <v>660.04</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>040500024</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5">
         <v>1817.88</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>04290102B</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5">
         <v>220.38</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>E094A1</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5">
         <v>975.91</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>070001194</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>71.40000000000001</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>070001196</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5">
+        <v>71.400000000000006</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5">
         <v>1694.79</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>F40701</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>784.3099999999999</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>C442B2</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5">
+        <v>784.31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5">
         <v>899.58</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>L17801</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5">
         <v>132</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>030404024</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5">
         <v>1467.31</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>050200510</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5">
         <v>1782</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>L19201</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5">
         <v>951.62</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>052701001</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5">
         <v>1142.54</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>N101301</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="5">
         <v>1183.95</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>070001213</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5">
         <v>354.99</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>080203144</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>608.1900000000001</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>F40501</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="5">
+        <v>608.19000000000005</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="5">
         <v>290.26</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>070100054</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
+    <row r="26" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="5">
         <v>1658.59</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>050502058</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="5">
         <v>209.01</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>050200944</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="5">
         <v>1586.78</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>080203119</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="5">
         <v>830.41</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>080203118</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="5">
         <v>782.08</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>080203116</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="5">
         <v>975.76</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>070001165</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="5">
         <v>809.96</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>050502037</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="5">
         <v>1347.93</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>070001195</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="n">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="5">
         <v>844.37</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>N80601</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="n">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="5">
         <v>1580.09</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>070001092</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="5">
         <v>982.39</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>020202351</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="n">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="5">
         <v>13.3</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>052700001</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="n">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="5">
         <v>1261.81</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>N722A1</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="n">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="5">
         <v>1167.5</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>04388018A</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="n">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="5">
         <v>1231.31</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>F06901</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="5">
         <v>432.02</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>050502001</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="5">
         <v>1570.36</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>04327100A</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="5">
         <v>709</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>F241A2</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="n">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="5">
         <v>513.66</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>080203142</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="n">
-        <v>969.6900000000001</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>080202012</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="n">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45" s="5">
+        <v>969.69</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="5">
         <v>1398.27</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>020303091</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="n">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" s="5">
         <v>1425.26</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>080203141</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="n">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" s="5">
         <v>1540.5</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>F40401</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="n">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B49" s="5">
         <v>1516.56</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>F169I2</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="n">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B50" s="5">
         <v>1189.46</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>OBM000240</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="n">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B51" s="5">
         <v>10.78</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>OBM000001</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="n">
-        <v>706.3099999999999</v>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B52" s="5">
+        <v>706.31</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>